--- a/src/nodes/HPC/compressor_stage_2_blade_rotor_coordinates_foil.xlsx
+++ b/src/nodes/HPC/compressor_stage_2_blade_rotor_coordinates_foil.xlsx
@@ -357,7 +357,7 @@
         <v>0.0012235617605994183</v>
       </c>
       <c r="B2">
-        <v>0.0013947067520054242</v>
+        <v>0.0013222718957779387</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -365,7 +365,7 @@
         <v>0.0024471235211988365</v>
       </c>
       <c r="B3">
-        <v>0.0020972806236092233</v>
+        <v>0.0019974379839443109</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -373,7 +373,7 @@
         <v>0.0036706852817982548</v>
       </c>
       <c r="B4">
-        <v>0.0026893113927942097</v>
+        <v>0.0025683256059061388</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -381,7 +381,7 @@
         <v>0.0048942470423976731</v>
       </c>
       <c r="B5">
-        <v>0.0032032438955131651</v>
+        <v>0.0030652261289175506</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -389,7 +389,7 @@
         <v>0.0061178088029970904</v>
       </c>
       <c r="B6">
-        <v>0.0036523713200178492</v>
+        <v>0.0035005554165604578</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -397,7 +397,7 @@
         <v>0.00734137056359651</v>
       </c>
       <c r="B7">
-        <v>0.0040443203114583154</v>
+        <v>0.003881439769887321</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -405,7 +405,7 @@
         <v>0.0085649323241959278</v>
       </c>
       <c r="B8">
-        <v>0.0043836131984157159</v>
+        <v>0.0042121077430852189</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -413,7 +413,7 @@
         <v>0.0097884940847953461</v>
       </c>
       <c r="B9">
-        <v>0.0046772524267657952</v>
+        <v>0.00449910183442252</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -421,7 +421,7 @@
         <v>0.011012055845394763</v>
       </c>
       <c r="B10">
-        <v>0.0049327859099329591</v>
+        <v>0.0047494732490453604</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -429,7 +429,7 @@
         <v>0.012235617605994181</v>
       </c>
       <c r="B11">
-        <v>0.0051574633142416788</v>
+        <v>0.004969994075529679</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -437,7 +437,7 @@
         <v>0.013459179366593601</v>
       </c>
       <c r="B12">
-        <v>0.0053551843424815473</v>
+        <v>0.0051643094042042557</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -445,7 +445,7 @@
         <v>0.014682741127193019</v>
       </c>
       <c r="B13">
-        <v>0.0055167470904025758</v>
+        <v>0.005323835448979429</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -453,7 +453,7 @@
         <v>0.015906302887792437</v>
       </c>
       <c r="B14">
-        <v>0.0056366674370887321</v>
+        <v>0.0054434579932527679</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -461,7 +461,7 @@
         <v>0.017129864648391856</v>
       </c>
       <c r="B15">
-        <v>0.0057374340019993812</v>
+        <v>0.0055441699747891815</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -469,7 +469,7 @@
         <v>0.01835342640899127</v>
       </c>
       <c r="B16">
-        <v>0.0058396730404362256</v>
+        <v>0.0056452258166855155</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -477,7 +477,7 @@
         <v>0.019576988169590692</v>
       </c>
       <c r="B17">
-        <v>0.0059285886106949133</v>
+        <v>0.0057328187289990068</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -485,7 +485,7 @@
         <v>0.02080054993019011</v>
       </c>
       <c r="B18">
-        <v>0.0059850586572798422</v>
+        <v>0.0057891038220404386</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -493,7 +493,7 @@
         <v>0.022024111690789525</v>
       </c>
       <c r="B19">
-        <v>0.0060080788665364607</v>
+        <v>0.0058131450201743817</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -501,7 +501,7 @@
         <v>0.023247673451388947</v>
       </c>
       <c r="B20">
-        <v>0.0060011743602704781</v>
+        <v>0.0058082334512788514</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -509,7 +509,7 @@
         <v>0.024471235211988362</v>
       </c>
       <c r="B21">
-        <v>0.0059678702602876076</v>
+        <v>0.0057776602432318648</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -517,7 +517,7 @@
         <v>0.02569479697258778</v>
       </c>
       <c r="B22">
-        <v>0.0059110621488534737</v>
+        <v>0.00572412862217312</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -525,7 +525,7 @@
         <v>0.026918358733187202</v>
       </c>
       <c r="B23">
-        <v>0.0058311274500733572</v>
+        <v>0.0056479902072890421</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -533,7 +533,7 @@
         <v>0.02814192049378662</v>
       </c>
       <c r="B24">
-        <v>0.0057278140485124548</v>
+        <v>0.0055490087160277408</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -541,7 +541,7 @@
         <v>0.029365482254386038</v>
       </c>
       <c r="B25">
-        <v>0.005600869828735964</v>
+        <v>0.0054269478658373217</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -549,7 +549,7 @@
         <v>0.030589044014985453</v>
       </c>
       <c r="B26">
-        <v>0.0054499352127722724</v>
+        <v>0.0052814707513406511</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -557,7 +557,7 @@
         <v>0.031812605775584875</v>
       </c>
       <c r="B27">
-        <v>0.005274220772502526</v>
+        <v>0.0051118379758596233</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -565,7 +565,7 @@
         <v>0.03303616753618429</v>
       </c>
       <c r="B28">
-        <v>0.0050728296172710633</v>
+        <v>0.0049172095198908895</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -573,7 +573,7 @@
         <v>0.034259729296783711</v>
       </c>
       <c r="B29">
-        <v>0.0048448648564222221</v>
+        <v>0.0046967453639311</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -581,7 +581,7 @@
         <v>0.035483291057383126</v>
       </c>
       <c r="B30">
-        <v>0.00458989044439998</v>
+        <v>0.0044500352673430893</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -589,7 +589,7 @@
         <v>0.036706852817982541</v>
       </c>
       <c r="B31">
-        <v>0.0043093137160468637</v>
+        <v>0.0041783881049544131</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -597,7 +597,7 @@
         <v>0.037930414578581963</v>
       </c>
       <c r="B32">
-        <v>0.0040050028513050383</v>
+        <v>0.0038835425304588052</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -605,7 +605,7 @@
         <v>0.039153976339181384</v>
       </c>
       <c r="B33">
-        <v>0.00367882603011667</v>
+        <v>0.0035672371975500028</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -613,7 +613,7 @@
         <v>0.0403775380997808</v>
       </c>
       <c r="B34">
-        <v>0.003331893648450158</v>
+        <v>0.0032305031052734046</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -621,7 +621,7 @@
         <v>0.041601099860380221</v>
       </c>
       <c r="B35">
-        <v>0.0029622849663788337</v>
+        <v>0.002871540634081056</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -629,7 +629,7 @@
         <v>0.042824661620979636</v>
       </c>
       <c r="B36">
-        <v>0.0025673214600022624</v>
+        <v>0.002487842509776665</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -637,7 +637,7 @@
         <v>0.044048223381579051</v>
       </c>
       <c r="B37">
-        <v>0.0021443246054200053</v>
+        <v>0.0020769014581639347</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -645,7 +645,7 @@
         <v>0.045271785142178472</v>
       </c>
       <c r="B38">
-        <v>0.0016887653595593554</v>
+        <v>0.0016344826660668276</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -653,7 +653,7 @@
         <v>0.046495346902777894</v>
       </c>
       <c r="B39">
-        <v>0.0011887126026585175</v>
+        <v>0.0011494411643903186</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -661,7 +661,7 @@
         <v>0.047718908663377309</v>
       </c>
       <c r="B40">
-        <v>0.00063038469578342415</v>
+        <v>0.00060890444505963591</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -677,7 +677,7 @@
         <v>0.048942470423976724</v>
       </c>
       <c r="B42">
-        <v>1.0858125391113857E-17</v>
+        <v>1.0878024215899037E-17</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -685,7 +685,7 @@
         <v>0.047718908663377309</v>
       </c>
       <c r="B43">
-        <v>-1.402282593022381E-05</v>
+        <v>7.4574247935645775E-06</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -693,7 +693,7 @@
         <v>0.046495346902777894</v>
       </c>
       <c r="B44">
-        <v>1.0569454612552061E-05</v>
+        <v>4.9840892880751E-05</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -701,7 +701,7 @@
         <v>0.045271785142178472</v>
       </c>
       <c r="B45">
-        <v>6.0284554783528458E-05</v>
+        <v>0.00011456724827605606</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -709,7 +709,7 @@
         <v>0.044048223381579051</v>
       </c>
       <c r="B46">
-        <v>0.00012163018773789523</v>
+        <v>0.00018905333499396555</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -717,7 +717,7 @@
         <v>0.042824661620979636</v>
       </c>
       <c r="B47">
-        <v>0.00018295295323433595</v>
+        <v>0.00026243190345993347</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -725,7 +725,7 @@
         <v>0.041601099860380221</v>
       </c>
       <c r="B48">
-        <v>0.00023995499744550888</v>
+        <v>0.00033069932974328649</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -733,7 +733,7 @@
         <v>0.0403775380997808</v>
       </c>
       <c r="B49">
-        <v>0.00029017735314756671</v>
+        <v>0.00039156789632431994</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -741,7 +741,7 @@
         <v>0.039153976339181384</v>
       </c>
       <c r="B50">
-        <v>0.00033116105311666152</v>
+        <v>0.00044274988568332869</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -749,7 +749,7 @@
         <v>0.037930414578581963</v>
       </c>
       <c r="B51">
-        <v>0.00036119322591804046</v>
+        <v>0.00048265354676427387</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -757,7 +757,7 @@
         <v>0.036706852817982541</v>
       </c>
       <c r="B52">
-        <v>0.00038154538327333024</v>
+        <v>0.00051247099436578145</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -765,7 +765,7 @@
         <v>0.035483291057383126</v>
       </c>
       <c r="B53">
-        <v>0.00039423513269325254</v>
+        <v>0.00053409030975014337</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -773,7 +773,7 @@
         <v>0.034259729296783711</v>
       </c>
       <c r="B54">
-        <v>0.00040128008168852932</v>
+        <v>0.00054939957417965229</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -781,7 +781,7 @@
         <v>0.03303616753618429</v>
       </c>
       <c r="B55">
-        <v>0.00040422669586580453</v>
+        <v>0.00055984679324597977</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -789,7 +789,7 @@
         <v>0.031812605775584875</v>
       </c>
       <c r="B56">
-        <v>0.00040273687321541269</v>
+        <v>0.00056511966985831649</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -797,7 +797,7 @@
         <v>0.030589044014985453</v>
       </c>
       <c r="B57">
-        <v>0.00039600136982361058</v>
+        <v>0.00056446583125523283</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -805,7 +805,7 @@
         <v>0.029365482254386038</v>
       </c>
       <c r="B58">
-        <v>0.00038321094177665529</v>
+        <v>0.0005571329046752992</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -813,7 +813,7 @@
         <v>0.02814192049378662</v>
       </c>
       <c r="B59">
-        <v>0.0003636540739710046</v>
+        <v>0.00054245940645571979</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -821,7 +821,7 @@
         <v>0.026918358733187202</v>
       </c>
       <c r="B60">
-        <v>0.00033701016654392156</v>
+        <v>0.00052014740932823634</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -829,7 +829,7 @@
         <v>0.02569479697258778</v>
       </c>
       <c r="B61">
-        <v>0.00030305634844287021</v>
+        <v>0.00048998987512322391</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -837,7 +837,7 @@
         <v>0.024471235211988362</v>
       </c>
       <c r="B62">
-        <v>0.00026156974861531472</v>
+        <v>0.0004517797656710581</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -845,7 +845,7 @@
         <v>0.023247673451388947</v>
       </c>
       <c r="B63">
-        <v>0.00021294709052166257</v>
+        <v>0.00040588799951329007</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -853,7 +853,7 @@
         <v>0.022024111690789525</v>
       </c>
       <c r="B64">
-        <v>0.00016006347567409444</v>
+        <v>0.00035499732203617357</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -861,7 +861,7 @@
         <v>0.02080054993019011</v>
       </c>
       <c r="B65">
-        <v>0.00010641360009773462</v>
+        <v>0.00030236843533713842</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -869,7 +869,7 @@
         <v>0.019576988169590692</v>
       </c>
       <c r="B66">
-        <v>5.5492159817707039E-05</v>
+        <v>0.00025126204151361409</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -877,7 +877,7 @@
         <v>0.01835342640899127</v>
       </c>
       <c r="B67">
-        <v>6.2563279149180473E-06</v>
+        <v>0.00020070355166562843</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -885,7 +885,7 @@
         <v>0.017129864648391856</v>
       </c>
       <c r="B68">
-        <v>-6.0486814306597572E-05</v>
+        <v>0.00013277721290360183</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -893,7 +893,7 @@
         <v>0.015906302887792437</v>
       </c>
       <c r="B69">
-        <v>-0.00015961587799018346</v>
+        <v>3.3593565845780539E-05</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -901,7 +901,7 @@
         <v>0.014682741127193019</v>
       </c>
       <c r="B70">
-        <v>-0.00027060215229182276</v>
+        <v>-7.7690510868675959E-05</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -909,7 +909,7 @@
         <v>0.013459179366593601</v>
       </c>
       <c r="B71">
-        <v>-0.00037106380583722169</v>
+        <v>-0.00018018886755992916</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -917,7 +917,7 @@
         <v>0.012235617605994181</v>
       </c>
       <c r="B72">
-        <v>-0.00046661384711833354</v>
+        <v>-0.00027914460840633285</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -925,7 +925,7 @@
         <v>0.011012055845394763</v>
       </c>
       <c r="B73">
-        <v>-0.000566593916695012</v>
+        <v>-0.00038328125580741276</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -933,7 +933,7 @@
         <v>0.0097884940847953461</v>
       </c>
       <c r="B74">
-        <v>-0.00066726534353246365</v>
+        <v>-0.00048911475118918824</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -941,7 +941,7 @@
         <v>0.0085649323241959278</v>
       </c>
       <c r="B75">
-        <v>-0.00076155046149919015</v>
+        <v>-0.00059004500616869314</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -949,7 +949,7 @@
         <v>0.00734137056359651</v>
       </c>
       <c r="B76">
-        <v>-0.00084209593567152079</v>
+        <v>-0.00067921539410052592</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -957,7 +957,7 @@
         <v>0.0061178088029970904</v>
       </c>
       <c r="B77">
-        <v>-0.00090210578370388233</v>
+        <v>-0.000750289880246491</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -965,7 +965,7 @@
         <v>0.0048942470423976731</v>
       </c>
       <c r="B78">
-        <v>-0.00093728910235526478</v>
+        <v>-0.00079927133575965028</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -973,7 +973,7 @@
         <v>0.0036706852817982548</v>
       </c>
       <c r="B79">
-        <v>-0.0009402622138479041</v>
+        <v>-0.00081927642695983356</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -981,7 +981,7 @@
         <v>0.0024471235211988365</v>
       </c>
       <c r="B80">
-        <v>-0.00089799856633815129</v>
+        <v>-0.00079815592667323873</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -989,7 +989,7 @@
         <v>0.0012235617605994183</v>
       </c>
       <c r="B81">
-        <v>-0.00077833893481914207</v>
+        <v>-0.00070590407859165666</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1023,7 +1023,7 @@
         <v>0.001421998832129341</v>
       </c>
       <c r="B2">
-        <v>0.00065617362005076672</v>
+        <v>0.00051095909931371856</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1031,7 +1031,7 @@
         <v>0.0028439976642586819</v>
       </c>
       <c r="B3">
-        <v>0.00097856758185782</v>
+        <v>0.00077840702624729422</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1039,7 +1039,7 @@
         <v>0.0042659964963880229</v>
       </c>
       <c r="B4">
-        <v>0.0012487458442246593</v>
+        <v>0.001006198347426022</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1047,7 +1047,7 @@
         <v>0.0056879953285173639</v>
       </c>
       <c r="B5">
-        <v>0.0014823581263414341</v>
+        <v>0.0012056655935857069</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1055,7 +1055,7 @@
         <v>0.007109994160646704</v>
       </c>
       <c r="B6">
-        <v>0.001685784287213744</v>
+        <v>0.001381429798104374</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1063,7 +1063,7 @@
         <v>0.0085319929927760458</v>
       </c>
       <c r="B7">
-        <v>0.0018626653846210411</v>
+        <v>0.0015361289488015166</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1071,7 +1071,7 @@
         <v>0.0099539918249053859</v>
       </c>
       <c r="B8">
-        <v>0.0020151417520154853</v>
+        <v>0.001671314431900545</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1079,7 +1079,7 @@
         <v>0.011375990657034728</v>
       </c>
       <c r="B9">
-        <v>0.0021465601250442628</v>
+        <v>0.0017894108983666573</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1087,7 +1087,7 @@
         <v>0.012797989489164068</v>
       </c>
       <c r="B10">
-        <v>0.0022605339530021619</v>
+        <v>0.0018930360164807541</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1095,7 +1095,7 @@
         <v>0.014219988321293408</v>
       </c>
       <c r="B11">
-        <v>0.0023605371375793422</v>
+        <v>0.0019847062590447541</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1103,7 +1103,7 @@
         <v>0.01564198715342275</v>
       </c>
       <c r="B12">
-        <v>0.0024484237519890556</v>
+        <v>0.0020657652623304107</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1111,7 +1111,7 @@
         <v>0.017063985985552092</v>
       </c>
       <c r="B13">
-        <v>0.0025197081031415412</v>
+        <v>0.0021329665119677911</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1119,7 +1119,7 @@
         <v>0.01848598481768143</v>
       </c>
       <c r="B14">
-        <v>0.0025717071285833045</v>
+        <v>0.002184368514968925</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1127,7 +1127,7 @@
         <v>0.019907983649810772</v>
       </c>
       <c r="B15">
-        <v>0.0026152880547089278</v>
+        <v>0.0022278400145153759</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1135,7 +1135,7 @@
         <v>0.02132998248194011</v>
       </c>
       <c r="B16">
-        <v>0.0026604182482744586</v>
+        <v>0.0022705981826843438</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1143,7 +1143,7 @@
         <v>0.022751981314069455</v>
       </c>
       <c r="B17">
-        <v>0.0026999153486337293</v>
+        <v>0.0023074436709660312</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1151,7 +1151,7 @@
         <v>0.024173980146198797</v>
       </c>
       <c r="B18">
-        <v>0.0027245046218459632</v>
+        <v>0.0023316621566655082</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1159,7 +1159,7 @@
         <v>0.025595978978328136</v>
       </c>
       <c r="B19">
-        <v>0.0027336915681941739</v>
+        <v>0.0023428959409343042</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1167,7 +1167,7 @@
         <v>0.027017977810457477</v>
       </c>
       <c r="B20">
-        <v>0.0027291767465173217</v>
+        <v>0.0023423764808855642</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1175,7 +1175,7 @@
         <v>0.028439976642586816</v>
       </c>
       <c r="B21">
-        <v>0.0027126607156543678</v>
+        <v>0.0023313352336324323</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1183,7 +1183,7 @@
         <v>0.029861975474716158</v>
       </c>
       <c r="B22">
-        <v>0.0026855412938481373</v>
+        <v>0.0023107843895019478</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1191,7 +1191,7 @@
         <v>0.0312839743068455</v>
       </c>
       <c r="B23">
-        <v>0.0026480053369569148</v>
+        <v>0.0022808590716767263</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1199,7 +1199,7 @@
         <v>0.032705973138974845</v>
       </c>
       <c r="B24">
-        <v>0.0025999369602428503</v>
+        <v>0.002241475136553278</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1207,7 +1207,7 @@
         <v>0.034127971971104183</v>
       </c>
       <c r="B25">
-        <v>0.0025412202789680941</v>
+        <v>0.0021925484405281117</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1215,7 +1215,7 @@
         <v>0.035549970803233522</v>
       </c>
       <c r="B26">
-        <v>0.0024716894389705032</v>
+        <v>0.0021339585825553395</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1223,7 +1223,7 @@
         <v>0.03697196963536286</v>
       </c>
       <c r="B27">
-        <v>0.0023909787083907564</v>
+        <v>0.0020654401318194785</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1231,7 +1231,7 @@
         <v>0.038393968467492205</v>
       </c>
       <c r="B28">
-        <v>0.0022986723859452422</v>
+        <v>0.001986691400062648</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1239,7 +1239,7 @@
         <v>0.039815967299621544</v>
       </c>
       <c r="B29">
-        <v>0.0021943547703503472</v>
+        <v>0.0018974106990269672</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1247,7 +1247,7 @@
         <v>0.041237966131750889</v>
       </c>
       <c r="B30">
-        <v>0.0020778355223742642</v>
+        <v>0.0017974594221562986</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1255,7 +1255,7 @@
         <v>0.04265996496388022</v>
       </c>
       <c r="B31">
-        <v>0.0019498257509924116</v>
+        <v>0.0016873512897014784</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1263,7 +1263,7 @@
         <v>0.044081963796009566</v>
       </c>
       <c r="B32">
-        <v>0.001811261927232011</v>
+        <v>0.0015677631036150853</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1271,7 +1271,7 @@
         <v>0.045503962628138911</v>
       </c>
       <c r="B33">
-        <v>0.0016630805221202868</v>
+        <v>0.0014393716658496988</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1279,7 +1279,7 @@
         <v>0.046925961460268249</v>
       </c>
       <c r="B34">
-        <v>0.0015058535822902587</v>
+        <v>0.0013025898512428519</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1287,7 +1287,7 @@
         <v>0.048347960292397595</v>
       </c>
       <c r="B35">
-        <v>0.0013386954567981325</v>
+        <v>0.0011567748261718924</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1295,7 +1295,7 @@
         <v>0.049769959124526926</v>
       </c>
       <c r="B36">
-        <v>0.0011603560703059106</v>
+        <v>0.0010010198298991211</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1303,7 +1303,7 @@
         <v>0.051191957956656271</v>
       </c>
       <c r="B37">
-        <v>0.00096958534747559378</v>
+        <v>0.0008344181016868386</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1311,7 +1311,7 @@
         <v>0.05261395678878561</v>
       </c>
       <c r="B38">
-        <v>0.00076423965693772427</v>
+        <v>0.00065541587056783571</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1319,7 +1319,7 @@
         <v>0.054035955620914955</v>
       </c>
       <c r="B39">
-        <v>0.00053860114319700112</v>
+        <v>0.00045987132465686106</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1327,7 +1327,7 @@
         <v>0.055457954453044293</v>
       </c>
       <c r="B40">
-        <v>0.00028605839472666293</v>
+        <v>0.00024299564183915252</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1343,7 +1343,7 @@
         <v>0.056879953285173632</v>
       </c>
       <c r="B42">
-        <v>-5.0525713958334726E-17</v>
+        <v>-5.0519547021442463E-17</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -1351,7 +1351,7 @@
         <v>0.055457954453044293</v>
       </c>
       <c r="B43">
-        <v>-2.5990539240803171E-05</v>
+        <v>1.7072213646707149E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1359,7 +1359,7 @@
         <v>0.054035955620914955</v>
       </c>
       <c r="B44">
-        <v>-3.1904788253289367E-05</v>
+        <v>4.6825030286850705E-05</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1367,7 +1367,7 @@
         <v>0.05261395678878561</v>
       </c>
       <c r="B45">
-        <v>-2.4338505162917492E-05</v>
+        <v>8.4485281206971041E-05</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1375,7 +1375,7 @@
         <v>0.051191957956656271</v>
       </c>
       <c r="B46">
-        <v>-9.8874480950960917E-06</v>
+        <v>0.00012527979769365907</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1383,7 +1383,7 @@
         <v>0.049769959124526926</v>
       </c>
       <c r="B47">
-        <v>5.7456325755526075E-06</v>
+        <v>0.00016508187298234193</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1391,7 +1391,7 @@
         <v>0.048347960292397595</v>
       </c>
       <c r="B48">
-        <v>2.0430017477551567E-05</v>
+        <v>0.0002023506481037917</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1399,7 +1399,7 @@
         <v>0.046925961460268249</v>
       </c>
       <c r="B49">
-        <v>3.2927994990210292E-05</v>
+        <v>0.00023619172603761698</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1407,7 +1407,7 @@
         <v>0.045503962628138911</v>
       </c>
       <c r="B50">
-        <v>4.200185349283807E-05</v>
+        <v>0.000265710709763426</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1415,7 +1415,7 @@
         <v>0.044081963796009566</v>
       </c>
       <c r="B51">
-        <v>4.6777698123853665E-05</v>
+        <v>0.00029027652174077939</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1423,7 +1423,7 @@
         <v>0.04265996496388022</v>
       </c>
       <c r="B52">
-        <v>4.7836901058113493E-05</v>
+        <v>0.00031031136234904656</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1431,7 +1431,7 @@
         <v>0.041237966131750889</v>
       </c>
       <c r="B53">
-        <v>4.6124651229583376E-05</v>
+        <v>0.00032650075144754928</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1439,7 +1439,7 @@
         <v>0.039815967299621544</v>
       </c>
       <c r="B54">
-        <v>4.2586137572229116E-05</v>
+        <v>0.00033953020889560936</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1447,7 +1447,7 @@
         <v>0.038393968467492205</v>
       </c>
       <c r="B55">
-        <v>3.7940604187310215E-05</v>
+        <v>0.00034992159006990478</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1455,7 +1455,7 @@
         <v>0.03697196963536286</v>
       </c>
       <c r="B56">
-        <v>3.2003515845260819E-05</v>
+        <v>0.00035754209241653924</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1463,7 +1463,7 @@
         <v>0.035549970803233522</v>
       </c>
       <c r="B57">
-        <v>2.4364392483808795E-05</v>
+        <v>0.00036209524889897261</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1471,7 +1471,7 @@
         <v>0.034127971971104183</v>
       </c>
       <c r="B58">
-        <v>1.4612754040682004E-05</v>
+        <v>0.00036328459248066491</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1479,7 +1479,7 @@
         <v>0.032705973138974845</v>
       </c>
       <c r="B59">
-        <v>2.3875132169620944E-06</v>
+        <v>0.00036084933690653468</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1487,7 +1487,7 @@
         <v>0.0312839743068455</v>
       </c>
       <c r="B60">
-        <v>-1.2474846232853557E-05</v>
+        <v>0.00035467141904733441</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1495,7 +1495,7 @@
         <v>0.029861975474716158</v>
       </c>
       <c r="B61">
-        <v>-3.00884477909137E-05</v>
+        <v>0.00034466845655527521</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1503,7 +1503,7 @@
         <v>0.028439976642586816</v>
       </c>
       <c r="B62">
-        <v>-5.0567414939367126E-05</v>
+        <v>0.00033075806708256819</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1511,7 +1511,7 @@
         <v>0.027017977810457477</v>
       </c>
       <c r="B63">
-        <v>-7.3723729075126035E-05</v>
+        <v>0.00031307653655663167</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1519,7 +1519,7 @@
         <v>0.025595978978328136</v>
       </c>
       <c r="B64">
-        <v>-9.8160803254156775E-05</v>
+        <v>0.00029263482400571279</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1527,7 +1527,7 @@
         <v>0.024173980146198797</v>
       </c>
       <c r="B65">
-        <v>-0.00012217990844718899</v>
+        <v>0.00027066255673326595</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1535,7 +1535,7 @@
         <v>0.022751981314069455</v>
       </c>
       <c r="B66">
-        <v>-0.00014408231562495252</v>
+        <v>0.00024838936204274551</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1543,7 +1543,7 @@
         <v>0.02132998248194011</v>
       </c>
       <c r="B67">
-        <v>-0.00016436483571188344</v>
+        <v>0.00022545522987823174</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1551,7 +1551,7 @@
         <v>0.019907983649810772</v>
       </c>
       <c r="B68">
-        <v>-0.00019230643944724338</v>
+        <v>0.00019514160074630816</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1559,7 +1559,7 @@
         <v>0.01848598481768143</v>
       </c>
       <c r="B69">
-        <v>-0.00023509441934698063</v>
+        <v>0.00015224419426739872</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1567,7 +1567,7 @@
         <v>0.017063985985552092</v>
       </c>
       <c r="B70">
-        <v>-0.00028276719521896394</v>
+        <v>0.00010397439595478582</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1575,7 +1575,7 @@
         <v>0.01564198715342275</v>
       </c>
       <c r="B71">
-        <v>-0.00032446385423300582</v>
+        <v>5.8194635425638639E-05</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1583,7 +1583,7 @@
         <v>0.014219988321293408</v>
       </c>
       <c r="B72">
-        <v>-0.00036287502571477143</v>
+        <v>1.2955852819816198E-05</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1591,7 +1591,7 @@
         <v>0.012797989489164068</v>
       </c>
       <c r="B73">
-        <v>-0.00040249457251528289</v>
+        <v>-3.4996635993875635E-05</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1599,7 +1599,7 @@
         <v>0.011375990657034728</v>
       </c>
       <c r="B74">
-        <v>-0.00044147774943113782</v>
+        <v>-8.432852275353261E-05</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1607,7 +1607,7 @@
         <v>0.0099539918249053859</v>
       </c>
       <c r="B75">
-        <v>-0.00047636056765799488</v>
+        <v>-0.00013253324754305471</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1615,7 +1615,7 @@
         <v>0.0085319929927760458</v>
       </c>
       <c r="B76">
-        <v>-0.00050354067204218191</v>
+        <v>-0.00017700423622265713</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1623,7 +1623,7 @@
         <v>0.007109994160646704</v>
       </c>
       <c r="B77">
-        <v>-0.00051968302517299526</v>
+        <v>-0.00021532853606362519</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1631,7 +1631,7 @@
         <v>0.0056879953285173639</v>
       </c>
       <c r="B78">
-        <v>-0.00052266022696093636</v>
+        <v>-0.00024596769420520914</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1639,7 +1639,7 @@
         <v>0.0042659964963880229</v>
       </c>
       <c r="B79">
-        <v>-0.000508844712287206</v>
+        <v>-0.00026629721548856875</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1647,7 +1647,7 @@
         <v>0.0028439976642586819</v>
       </c>
       <c r="B80">
-        <v>-0.00047187122691410725</v>
+        <v>-0.00027171067130358134</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1655,7 +1655,7 @@
         <v>0.001421998832129341</v>
       </c>
       <c r="B81">
-        <v>-0.00039610551572494539</v>
+        <v>-0.00025089099498789717</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1689,7 +1689,7 @@
         <v>0.0015906302887792438</v>
       </c>
       <c r="B2">
-        <v>0.00043197152503949654</v>
+        <v>0.00031426488366983248</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1697,7 +1697,7 @@
         <v>0.0031812605775584876</v>
       </c>
       <c r="B3">
-        <v>0.000640383214312956</v>
+        <v>0.00047813892485747318</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1705,7 +1705,7 @@
         <v>0.0047718908663377316</v>
       </c>
       <c r="B4">
-        <v>0.00081420339919495736</v>
+        <v>0.00061760149550184275</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1713,7 +1713,7 @@
         <v>0.0063625211551169751</v>
       </c>
       <c r="B5">
-        <v>0.00096393161331587585</v>
+        <v>0.00073965274259800244</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1721,7 +1721,7 @@
         <v>0.0079531514438962187</v>
       </c>
       <c r="B6">
-        <v>0.0010938461134620818</v>
+        <v>0.00084714527034382133</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>0.0095437817326754631</v>
       </c>
       <c r="B7">
-        <v>0.0012063872790221428</v>
+        <v>0.00094170639896927661</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1737,7 +1737,7 @@
         <v>0.011134412021454708</v>
       </c>
       <c r="B8">
-        <v>0.0013029884130611529</v>
+        <v>0.0010242920481490954</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1745,7 +1745,7 @@
         <v>0.01272504231023395</v>
       </c>
       <c r="B9">
-        <v>0.0013858928045416645</v>
+        <v>0.0010963980919838417</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1753,7 +1753,7 @@
         <v>0.014315672599013195</v>
       </c>
       <c r="B10">
-        <v>0.0014575228974504633</v>
+        <v>0.0011596398235081146</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1761,7 +1761,7 @@
         <v>0.015906302887792437</v>
       </c>
       <c r="B11">
-        <v>0.0015202077699738154</v>
+        <v>0.0012155702570668147</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1769,7 +1769,7 @@
         <v>0.017496933176571684</v>
       </c>
       <c r="B12">
-        <v>0.0015751894926784541</v>
+        <v>0.0012650177179778538</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1777,7 +1777,7 @@
         <v>0.019087563465350926</v>
       </c>
       <c r="B13">
-        <v>0.0016194554714534998</v>
+        <v>0.0013059740541408866</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>0.020678193754130169</v>
       </c>
       <c r="B14">
-        <v>0.0016512031009942091</v>
+        <v>0.0013372377547607678</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1793,7 +1793,7 @@
         <v>0.022268824042909415</v>
       </c>
       <c r="B15">
-        <v>0.0016777243958979878</v>
+        <v>0.0013636703516814138</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1801,7 +1801,7 @@
         <v>0.023859454331688658</v>
       </c>
       <c r="B16">
-        <v>0.0017057075574251534</v>
+        <v>0.0013897308188302491</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1809,7 +1809,7 @@
         <v>0.0254500846204679</v>
       </c>
       <c r="B17">
-        <v>0.0017303309135855182</v>
+        <v>0.0014122048558296693</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1817,7 +1817,7 @@
         <v>0.027040714909247147</v>
       </c>
       <c r="B18">
-        <v>0.0017453686616020004</v>
+        <v>0.0014269420543379693</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1825,7 +1825,7 @@
         <v>0.028631345198026389</v>
       </c>
       <c r="B19">
-        <v>0.001750488348800445</v>
+        <v>0.0014337208484620665</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1833,7 +1833,7 @@
         <v>0.030221975486805632</v>
       </c>
       <c r="B20">
-        <v>0.001746830860032429</v>
+        <v>0.0014333018829210348</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1841,7 +1841,7 @@
         <v>0.031812605775584875</v>
       </c>
       <c r="B21">
-        <v>0.0017355370801495295</v>
+        <v>0.0014264458024339467</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1849,7 +1849,7 @@
         <v>0.033403236064364121</v>
       </c>
       <c r="B22">
-        <v>0.0017175448559243892</v>
+        <v>0.0014137778750688147</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1857,7 +1857,7 @@
         <v>0.034993866353143367</v>
       </c>
       <c r="B23">
-        <v>0.0016929798818139154</v>
+        <v>0.0013953818622894042</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1865,7 +1865,7 @@
         <v>0.036584496641922613</v>
       </c>
       <c r="B24">
-        <v>0.0016617648141960813</v>
+        <v>0.0013712061489084191</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1873,7 +1873,7 @@
         <v>0.038175126930701853</v>
       </c>
       <c r="B25">
-        <v>0.0016238223094488596</v>
+        <v>0.0013411991197385634</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1881,7 +1881,7 @@
         <v>0.039765757219481092</v>
       </c>
       <c r="B26">
-        <v>0.0015790416286171666</v>
+        <v>0.0013052868787907807</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1889,7 +1889,7 @@
         <v>0.041356387508260338</v>
       </c>
       <c r="B27">
-        <v>0.0015271784514136874</v>
+        <v>0.0012633064068689687</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1897,7 +1897,7 @@
         <v>0.042947017797039584</v>
       </c>
       <c r="B28">
-        <v>0.0014679550622180508</v>
+        <v>0.001215072403975266</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1905,7 +1905,7 @@
         <v>0.04453764808581883</v>
       </c>
       <c r="B29">
-        <v>0.001401093745409885</v>
+        <v>0.00116039957011181</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1913,7 +1913,7 @@
         <v>0.046128278374598077</v>
       </c>
       <c r="B30">
-        <v>0.0013264681812436025</v>
+        <v>0.0010992035185261549</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1921,7 +1921,7 @@
         <v>0.047718908663377316</v>
       </c>
       <c r="B31">
-        <v>0.0012445576334727546</v>
+        <v>0.0010318035154475214</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1929,7 +1929,7 @@
         <v>0.049309538952156555</v>
       </c>
       <c r="B32">
-        <v>0.0011559927617256747</v>
+        <v>0.0009586197403505457</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1937,7 +1937,7 @@
         <v>0.0509001692409358</v>
       </c>
       <c r="B33">
-        <v>0.0010614042256306988</v>
+        <v>0.0008800723727098649</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1945,7 +1945,7 @@
         <v>0.052490799529715047</v>
       </c>
       <c r="B34">
-        <v>0.000961178250655178</v>
+        <v>0.00079641861799295414</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1953,7 +1953,7 @@
         <v>0.054081429818494293</v>
       </c>
       <c r="B35">
-        <v>0.00085472332562253083</v>
+        <v>0.00070726378563864222</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1961,7 +1961,7 @@
         <v>0.055672060107273533</v>
       </c>
       <c r="B36">
-        <v>0.000741203505195193</v>
+        <v>0.00061205021107859682</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1969,7 +1969,7 @@
         <v>0.057262690396052779</v>
       </c>
       <c r="B37">
-        <v>0.00061978284403559883</v>
+        <v>0.00051022022974448443</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1977,7 +1977,7 @@
         <v>0.058853320684832018</v>
       </c>
       <c r="B38">
-        <v>0.000489025820473008</v>
+        <v>0.00040081644354765072</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1985,7 +1985,7 @@
         <v>0.060443950973611264</v>
       </c>
       <c r="B39">
-        <v>0.00034509860750397666</v>
+        <v>0.00028128252031815347</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1993,7 +1993,7 @@
         <v>0.06203458126239051</v>
       </c>
       <c r="B40">
-        <v>0.00018356780179188464</v>
+        <v>0.00014866239436572869</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2017,7 +2017,7 @@
         <v>0.06203458126239051</v>
       </c>
       <c r="B43">
-        <v>-2.5864642765050971E-05</v>
+        <v>9.0407646611049867E-06</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2025,7 +2025,7 @@
         <v>0.060443950973611264</v>
       </c>
       <c r="B44">
-        <v>-3.7797915610962182E-05</v>
+        <v>2.6018171574860988E-05</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2033,7 +2033,7 @@
         <v>0.058853320684832018</v>
       </c>
       <c r="B45">
-        <v>-4.0230441079135767E-05</v>
+        <v>4.7978935846221569E-05</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2041,7 +2041,7 @@
         <v>0.057262690396052779</v>
       </c>
       <c r="B46">
-        <v>-3.7592841711087021E-05</v>
+        <v>7.1969772580027312E-05</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>0.055672060107273533</v>
       </c>
       <c r="B47">
-        <v>-3.3716259504383287E-05</v>
+        <v>9.5437034612212782E-05</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2057,7 +2057,7 @@
         <v>0.054081429818494293</v>
       </c>
       <c r="B48">
-        <v>-3.0033914280799962E-05</v>
+        <v>0.00011742562570308853</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2065,7 +2065,7 @@
         <v>0.052490799529715047</v>
       </c>
       <c r="B49">
-        <v>-2.7379545318164427E-05</v>
+        <v>0.00013738008734405933</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2073,7 +2073,7 @@
         <v>0.0509001692409358</v>
       </c>
       <c r="B50">
-        <v>-2.6586891894304104E-05</v>
+        <v>0.00015474496102652974</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2081,7 +2081,7 @@
         <v>0.049309538952156555</v>
       </c>
       <c r="B51">
-        <v>-2.8245366525099569E-05</v>
+        <v>0.00016912765485002954</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2089,7 +2089,7 @@
         <v>0.047718908663377316</v>
       </c>
       <c r="B52">
-        <v>-3.1967074678644041E-05</v>
+        <v>0.00018078704334658908</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2097,7 +2097,7 @@
         <v>0.046128278374598077</v>
       </c>
       <c r="B53">
-        <v>-3.7119795061083892E-05</v>
+        <v>0.00019014486765636389</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2105,7 +2105,7 @@
         <v>0.04453764808581883</v>
       </c>
       <c r="B54">
-        <v>-4.3071306378565558E-05</v>
+        <v>0.00019762286891950961</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2113,7 +2113,7 @@
         <v>0.042947017797039584</v>
       </c>
       <c r="B55">
-        <v>-4.93408872386585E-05</v>
+        <v>0.00020354177100412649</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2121,7 +2121,7 @@
         <v>0.041356387508260338</v>
       </c>
       <c r="B56">
-        <v>-5.6053815854624588E-05</v>
+        <v>0.0002078182286900942</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2129,7 +2129,7 @@
         <v>0.039765757219481092</v>
       </c>
       <c r="B57">
-        <v>-6.3486870341148809E-05</v>
+        <v>0.00021026787948523723</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2137,7 +2137,7 @@
         <v>0.038175126930701853</v>
       </c>
       <c r="B58">
-        <v>-7.1916828812916092E-05</v>
+        <v>0.00021070636089738</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2145,7 +2145,7 @@
         <v>0.036584496641922613</v>
       </c>
       <c r="B59">
-        <v>-8.15871775298904E-05</v>
+        <v>0.00020897148775777169</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2153,7 +2153,7 @@
         <v>0.034993866353143367</v>
       </c>
       <c r="B60">
-        <v>-9.2608235333151192E-05</v>
+        <v>0.00020498978419136005</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2161,7 +2161,7 @@
         <v>0.033403236064364121</v>
       </c>
       <c r="B61">
-        <v>-0.00010505702920905695</v>
+        <v>0.00019870995164651757</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2169,7 +2169,7 @@
         <v>0.031812605775584875</v>
       </c>
       <c r="B62">
-        <v>-0.00011901058614396607</v>
+        <v>0.00019008069157161665</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2177,7 +2177,7 @@
         <v>0.030221975486805632</v>
       </c>
       <c r="B63">
-        <v>-0.00013434300263593651</v>
+        <v>0.00017918597447545787</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2185,7 +2185,7 @@
         <v>0.028631345198026389</v>
       </c>
       <c r="B64">
-        <v>-0.00015011665322982434</v>
+        <v>0.00016665084710855397</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2193,7 +2193,7 @@
         <v>0.027040714909247147</v>
       </c>
       <c r="B65">
-        <v>-0.00016519098198218508</v>
+        <v>0.00015323562528184591</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2201,7 +2201,7 @@
         <v>0.0254500846204679</v>
       </c>
       <c r="B66">
-        <v>-0.00017842543294957429</v>
+        <v>0.00013970062480627452</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2209,7 +2209,7 @@
         <v>0.023859454331688658</v>
       </c>
       <c r="B67">
-        <v>-0.00019015287414427196</v>
+        <v>0.00012582386445063231</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2217,7 +2217,7 @@
         <v>0.022268824042909415</v>
       </c>
       <c r="B68">
-        <v>-0.0002065998694014556</v>
+        <v>0.00010745417481511836</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2225,7 +2225,7 @@
         <v>0.020678193754130169</v>
       </c>
       <c r="B69">
-        <v>-0.00023258897640643868</v>
+        <v>8.1376369827002669E-05</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2233,7 +2233,7 @@
         <v>0.019087563465350926</v>
       </c>
       <c r="B70">
-        <v>-0.00026143303242218006</v>
+        <v>5.2048384890433354E-05</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2241,7 +2241,7 @@
         <v>0.017496933176571684</v>
       </c>
       <c r="B71">
-        <v>-0.00028584115552514631</v>
+        <v>2.4330619175453811E-05</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2249,7 +2249,7 @@
         <v>0.015906302887792437</v>
       </c>
       <c r="B72">
-        <v>-0.00030761730746818892</v>
+        <v>-2.9797945611881005E-06</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2257,7 +2257,7 @@
         <v>0.014315672599013195</v>
       </c>
       <c r="B73">
-        <v>-0.00032977554620362755</v>
+        <v>-3.1892472261278985E-05</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2265,7 +2265,7 @@
         <v>0.01272504231023395</v>
       </c>
       <c r="B74">
-        <v>-0.00035107547080526983</v>
+        <v>-6.1580758247447364E-05</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2273,7 +2273,7 @@
         <v>0.011134412021454708</v>
       </c>
       <c r="B75">
-        <v>-0.00036918977641119171</v>
+        <v>-9.0493411499134127E-05</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2281,7 +2281,7 @@
         <v>0.0095437817326754631</v>
       </c>
       <c r="B76">
-        <v>-0.00038169800129505416</v>
+        <v>-0.00011701712124218782</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2289,7 +2289,7 @@
         <v>0.0079531514438962187</v>
       </c>
       <c r="B77">
-        <v>-0.00038635894524748115</v>
+        <v>-0.00013965810212922052</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2297,7 +2297,7 @@
         <v>0.0063625211551169751</v>
       </c>
       <c r="B78">
-        <v>-0.00038174161099136406</v>
+        <v>-0.00015746274027349068</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2305,7 +2305,7 @@
         <v>0.0047718908663377316</v>
       </c>
       <c r="B79">
-        <v>-0.00036540802296372978</v>
+        <v>-0.00016880611927061527</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2313,7 +2313,7 @@
         <v>0.0031812605775584876</v>
       </c>
       <c r="B80">
-        <v>-0.00033308252241994086</v>
+        <v>-0.00017083823296445806</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2321,7 +2321,7 @@
         <v>0.0015906302887792438</v>
       </c>
       <c r="B81">
-        <v>-0.00027426832317848759</v>
+        <v>-0.00015656168180882356</v>
       </c>
     </row>
     <row r="82" spans="1:2">
